--- a/シナリオ.xlsx
+++ b/シナリオ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KentaroAoyama\Documents\Github\mufits\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KentaroAoyama\Documents\mufits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984E80AB-CA49-4404-B48B-D26DEF5FFF0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E29C75F0-0C0C-41FA-A95D-F619DEB1C019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{1F3EEEA8-185E-411F-9206-21CE91BFA886}"/>
+    <workbookView xWindow="13440" yWindow="1845" windowWidth="13710" windowHeight="11295" xr2:uid="{1F3EEEA8-185E-411F-9206-21CE91BFA886}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="84">
   <si>
     <t>流量</t>
   </si>
@@ -150,9 +150,6 @@
   </si>
   <si>
     <t>230℃</t>
-  </si>
-  <si>
-    <t>Unrest</t>
   </si>
   <si>
     <t>Q=10,000</t>
@@ -325,6 +322,87 @@
   </si>
   <si>
     <t>RUNNING (675→2000)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>可逆性</t>
+    <rPh sb="0" eb="2">
+      <t>カギャク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>セイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>可逆</t>
+    <rPh sb="0" eb="2">
+      <t>カギャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>破壊強度</t>
+    <rPh sb="0" eb="4">
+      <t>ハカイキョウド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>非可逆</t>
+    <rPh sb="0" eb="3">
+      <t>ヒカギャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2.7 (静水圧)</t>
+    <rPh sb="5" eb="8">
+      <t>セイスイアツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1 (変質岩の破壊強度の下限)</t>
+    <rPh sb="3" eb="5">
+      <t>ヘンシツ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>イワ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ハカイキョウド</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不安定化開始</t>
+    <rPh sb="0" eb="4">
+      <t>フアンテイカ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カイシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不安定化開始（capventの物性の変化）</t>
+    <rPh sb="0" eb="6">
+      <t>フアンテイカカイシ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ブッセイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヘンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RUNNING</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -405,7 +483,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -418,11 +496,17 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -757,40 +841,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C780DBF0-A8F5-4FC9-8C5F-407B8246C5E1}">
-  <dimension ref="A1:T38"/>
+  <dimension ref="A1:W44"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="5" max="5" width="17.25" customWidth="1"/>
     <col min="6" max="6" width="20.5" customWidth="1"/>
+    <col min="7" max="7" width="8.5" style="12" customWidth="1"/>
+    <col min="8" max="8" width="7.375" style="12" customWidth="1"/>
+    <col min="9" max="9" width="8.625" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="H1" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="O1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-    </row>
-    <row r="2" spans="1:20" ht="75" x14ac:dyDescent="0.4">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="K1" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="R1" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+    </row>
+    <row r="2" spans="1:23" ht="75" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -809,44 +899,47 @@
       <c r="F2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="K2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" s="1" t="s">
+      <c r="M2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="O2" s="1" t="s">
+      <c r="R2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q2" s="1" t="s">
+      <c r="T2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="T2" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>900</v>
       </c>
@@ -865,20 +958,20 @@
       <c r="F3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
       <c r="S3" s="5"/>
       <c r="T3" s="5"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>900</v>
       </c>
@@ -897,20 +990,20 @@
       <c r="F4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
       <c r="T4" s="5"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>900</v>
       </c>
@@ -927,22 +1020,22 @@
         <v>16</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
+        <v>55</v>
+      </c>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
       <c r="T5" s="5"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>900</v>
       </c>
@@ -961,20 +1054,20 @@
       <c r="F6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5"/>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>900</v>
       </c>
@@ -993,20 +1086,20 @@
       <c r="F7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
       <c r="O7" s="5"/>
       <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
       <c r="S7" s="5"/>
       <c r="T7" s="5"/>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>900</v>
       </c>
@@ -1023,22 +1116,22 @@
         <v>16</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
+        <v>56</v>
+      </c>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
       <c r="S8" s="5"/>
       <c r="T8" s="5"/>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="5"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>900</v>
       </c>
@@ -1057,36 +1150,36 @@
       <c r="F9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="O9" t="s">
-        <v>59</v>
-      </c>
-      <c r="P9" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>59</v>
-      </c>
+      <c r="K9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
       <c r="R9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.4">
+        <v>58</v>
+      </c>
+      <c r="U9" t="s">
+        <v>58</v>
+      </c>
+      <c r="V9" t="s">
+        <v>58</v>
+      </c>
+      <c r="W9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>900</v>
       </c>
@@ -1105,32 +1198,32 @@
       <c r="F10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="I10" s="6" t="s">
+      <c r="K10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="M10" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="N10" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="O10" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="P10" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
       <c r="S10" s="5"/>
       <c r="T10" s="5"/>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+      <c r="W10" s="5"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>900</v>
       </c>
@@ -1149,32 +1242,32 @@
       <c r="F11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="I11" s="6" t="s">
+      <c r="K11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M11" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="N11" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="K11" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="L11" t="s">
-        <v>73</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
+      <c r="O11" t="s">
+        <v>72</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>69</v>
+      </c>
       <c r="R11" s="5"/>
       <c r="S11" s="5"/>
       <c r="T11" s="5"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>900</v>
       </c>
@@ -1193,20 +1286,20 @@
       <c r="F12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
       <c r="O12" s="5"/>
       <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
       <c r="R12" s="5"/>
       <c r="S12" s="5"/>
       <c r="T12" s="5"/>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U12" s="5"/>
+      <c r="V12" s="5"/>
+      <c r="W12" s="5"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>900</v>
       </c>
@@ -1225,32 +1318,32 @@
       <c r="F13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="J13" s="10" t="s">
+      <c r="K13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="L13" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="K13" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="L13" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="M13" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
+      <c r="M13" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>70</v>
+      </c>
       <c r="R13" s="5"/>
       <c r="S13" s="5"/>
       <c r="T13" s="5"/>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>900</v>
       </c>
@@ -1269,20 +1362,20 @@
       <c r="F14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="K14" t="s">
+        <v>73</v>
+      </c>
+      <c r="L14" t="s">
         <v>74</v>
       </c>
-      <c r="I14" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
       <c r="R14" s="5"/>
       <c r="S14" s="5"/>
       <c r="T14" s="5"/>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+      <c r="W14" s="5"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>900</v>
       </c>
@@ -1301,14 +1394,14 @@
       <c r="F15" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="K15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L15" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.4">
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>900</v>
       </c>
@@ -1327,18 +1420,18 @@
       <c r="F16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H16" s="5"/>
-      <c r="I16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="R16" s="5"/>
       <c r="S16" s="5"/>
       <c r="T16" s="5"/>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+      <c r="W16" s="5"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>900</v>
       </c>
@@ -1357,18 +1450,18 @@
       <c r="F17" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H17" s="5"/>
-      <c r="I17" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="6" t="s">
+        <v>46</v>
+      </c>
       <c r="R17" s="5"/>
       <c r="S17" s="5"/>
       <c r="T17" s="5"/>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U17" s="5"/>
+      <c r="V17" s="5"/>
+      <c r="W17" s="5"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>900</v>
       </c>
@@ -1387,12 +1480,12 @@
       <c r="F18" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="5"/>
-      <c r="I18" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="K18" s="5"/>
+      <c r="L18" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>900</v>
       </c>
@@ -1411,18 +1504,18 @@
       <c r="F19" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H19" s="5"/>
-      <c r="I19" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="R19" s="5"/>
       <c r="S19" s="5"/>
       <c r="T19" s="5"/>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+      <c r="W19" s="5"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>900</v>
       </c>
@@ -1441,18 +1534,18 @@
       <c r="F20" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="5"/>
-      <c r="I20" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="R20" s="5"/>
       <c r="S20" s="5"/>
       <c r="T20" s="5"/>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+      <c r="W20" s="5"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>900</v>
       </c>
@@ -1471,20 +1564,20 @@
       <c r="F21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
       <c r="R21" s="5"/>
       <c r="S21" s="5"/>
       <c r="T21" s="5"/>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>900</v>
       </c>
@@ -1503,20 +1596,20 @@
       <c r="F22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
       <c r="O22" s="5"/>
       <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
       <c r="R22" s="5"/>
       <c r="S22" s="5"/>
       <c r="T22" s="5"/>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
+      <c r="W22" s="5"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>900</v>
       </c>
@@ -1533,18 +1626,18 @@
         <v>16</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
+        <v>57</v>
+      </c>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
       <c r="R23" s="5"/>
       <c r="S23" s="5"/>
       <c r="T23" s="5"/>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U23" s="5"/>
+      <c r="V23" s="5"/>
+      <c r="W23" s="5"/>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>900</v>
       </c>
@@ -1563,20 +1656,20 @@
       <c r="F24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
       <c r="O24" s="5"/>
       <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
       <c r="R24" s="5"/>
       <c r="S24" s="5"/>
       <c r="T24" s="5"/>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U24" s="5"/>
+      <c r="V24" s="5"/>
+      <c r="W24" s="5"/>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>900</v>
       </c>
@@ -1595,20 +1688,20 @@
       <c r="F25" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
       <c r="O25" s="5"/>
       <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
       <c r="R25" s="5"/>
       <c r="S25" s="5"/>
       <c r="T25" s="5"/>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U25" s="5"/>
+      <c r="V25" s="5"/>
+      <c r="W25" s="5"/>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>900</v>
       </c>
@@ -1625,18 +1718,18 @@
         <v>16</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="O26" s="5"/>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="5"/>
+        <v>57</v>
+      </c>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
       <c r="R26" s="5"/>
       <c r="S26" s="5"/>
       <c r="T26" s="5"/>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U26" s="5"/>
+      <c r="V26" s="5"/>
+      <c r="W26" s="5"/>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>900</v>
       </c>
@@ -1655,20 +1748,20 @@
       <c r="F27" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
       <c r="K27" s="5"/>
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
       <c r="O27" s="5"/>
       <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
       <c r="R27" s="5"/>
       <c r="S27" s="5"/>
       <c r="T27" s="5"/>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U27" s="5"/>
+      <c r="V27" s="5"/>
+      <c r="W27" s="5"/>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>900</v>
       </c>
@@ -1687,20 +1780,20 @@
       <c r="F28" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H28" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
+      <c r="K28" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>46</v>
+      </c>
       <c r="R28" s="5"/>
       <c r="S28" s="5"/>
       <c r="T28" s="5"/>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U28" s="5"/>
+      <c r="V28" s="5"/>
+      <c r="W28" s="5"/>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>900</v>
       </c>
@@ -1719,20 +1812,20 @@
       <c r="F29" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H29" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5"/>
+      <c r="K29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="R29" s="5"/>
       <c r="S29" s="5"/>
       <c r="T29" s="5"/>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U29" s="5"/>
+      <c r="V29" s="5"/>
+      <c r="W29" s="5"/>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>900</v>
       </c>
@@ -1751,20 +1844,20 @@
       <c r="F30" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
       <c r="K30" s="5"/>
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
       <c r="O30" s="5"/>
       <c r="P30" s="5"/>
-      <c r="Q30" s="5"/>
       <c r="R30" s="5"/>
       <c r="S30" s="5"/>
       <c r="T30" s="5"/>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U30" s="5"/>
+      <c r="V30" s="5"/>
+      <c r="W30" s="5"/>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>900</v>
       </c>
@@ -1783,20 +1876,20 @@
       <c r="F31" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H31" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O31" s="5"/>
-      <c r="P31" s="5"/>
-      <c r="Q31" s="5"/>
+      <c r="K31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="R31" s="5"/>
       <c r="S31" s="5"/>
       <c r="T31" s="5"/>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U31" s="5"/>
+      <c r="V31" s="5"/>
+      <c r="W31" s="5"/>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>900</v>
       </c>
@@ -1815,20 +1908,20 @@
       <c r="F32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H32" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I32" s="2" t="s">
+      <c r="K32" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="O32" s="5"/>
-      <c r="P32" s="5"/>
-      <c r="Q32" s="5"/>
+      <c r="L32" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="R32" s="5"/>
       <c r="S32" s="5"/>
       <c r="T32" s="5"/>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U32" s="5"/>
+      <c r="V32" s="5"/>
+      <c r="W32" s="5"/>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>900</v>
       </c>
@@ -1847,14 +1940,14 @@
       <c r="F33" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H33" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="K33" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>900</v>
       </c>
@@ -1873,20 +1966,20 @@
       <c r="F34" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
       <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
       <c r="O34" s="5"/>
       <c r="P34" s="5"/>
-      <c r="Q34" s="5"/>
       <c r="R34" s="5"/>
       <c r="S34" s="5"/>
       <c r="T34" s="5"/>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U34" s="5"/>
+      <c r="V34" s="5"/>
+      <c r="W34" s="5"/>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>900</v>
       </c>
@@ -1905,20 +1998,20 @@
       <c r="F35" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
       <c r="K35" s="5"/>
       <c r="L35" s="5"/>
       <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
       <c r="O35" s="5"/>
       <c r="P35" s="5"/>
-      <c r="Q35" s="5"/>
       <c r="R35" s="5"/>
       <c r="S35" s="5"/>
       <c r="T35" s="5"/>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U35" s="5"/>
+      <c r="V35" s="5"/>
+      <c r="W35" s="5"/>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>900</v>
       </c>
@@ -1937,14 +2030,14 @@
       <c r="F36" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H36" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="K36" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>900</v>
       </c>
@@ -1963,18 +2056,18 @@
       <c r="F37" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H37" s="5"/>
-      <c r="I37" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="O37" s="5"/>
-      <c r="P37" s="5"/>
-      <c r="Q37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="R37" s="5"/>
       <c r="S37" s="5"/>
       <c r="T37" s="5"/>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="U37" s="5"/>
+      <c r="V37" s="5"/>
+      <c r="W37" s="5"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>900</v>
       </c>
@@ -1993,22 +2086,131 @@
       <c r="F38" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H38" s="5"/>
-      <c r="I38" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="O38" s="5"/>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="R38" s="5"/>
       <c r="S38" s="5"/>
       <c r="T38" s="5"/>
+      <c r="U38" s="5"/>
+      <c r="V38" s="5"/>
+      <c r="W38" s="5"/>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="K40" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="L40" s="9"/>
+      <c r="M40" s="9"/>
+      <c r="N40" s="9"/>
+      <c r="O40" s="9"/>
+      <c r="P40" s="9"/>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="H41" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="I41" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="P41" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="A42">
+        <v>900</v>
+      </c>
+      <c r="B42">
+        <v>0.1</v>
+      </c>
+      <c r="C42">
+        <v>10000</v>
+      </c>
+      <c r="D42">
+        <v>10</v>
+      </c>
+      <c r="E42" t="s">
+        <v>6</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="I42" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K42" t="s">
+        <v>83</v>
+      </c>
+      <c r="L42" t="s">
+        <v>83</v>
+      </c>
+      <c r="M42" t="s">
+        <v>83</v>
+      </c>
+      <c r="N42" t="s">
+        <v>83</v>
+      </c>
+      <c r="O42" t="s">
+        <v>83</v>
+      </c>
+      <c r="P42" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="H43" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="I43" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="K43" t="s">
+        <v>83</v>
+      </c>
+      <c r="P43" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.4">
+      <c r="H44" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I44" s="12">
+        <v>2.7</v>
+      </c>
+      <c r="K44" t="s">
+        <v>83</v>
+      </c>
+      <c r="P44" t="s">
+        <v>83</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="O1:T1"/>
+    <mergeCell ref="K1:P1"/>
+    <mergeCell ref="R1:W1"/>
+    <mergeCell ref="K40:P40"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
